--- a/relatorios/Controle_Horas_21-07-2026.xlsx
+++ b/relatorios/Controle_Horas_21-07-2026.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
